--- a/docs/ability/a1_ability_reference.xlsx
+++ b/docs/ability/a1_ability_reference.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="A1 rules" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Thresholds" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Logic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Logic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Thresholds" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Examples" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Results" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Results detail" sheetId="6" state="visible" r:id="rId6"/>
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,12 +67,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00274E13"/>
       <sz val="10"/>
     </font>
@@ -97,12 +91,24 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00262626"/>
+      <color rgb="001F3864"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="007F7F7F"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00262626"/>
       <sz val="10"/>
     </font>
     <font>
@@ -153,12 +159,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-        <bgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00A9D08E"/>
         <bgColor rgb="00A9D08E"/>
       </patternFill>
@@ -179,6 +179,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
         <bgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
@@ -206,7 +212,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -255,17 +261,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="00D9D9D9"/>
       </right>
@@ -298,32 +293,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -333,55 +302,83 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -458,6 +455,216 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Credit cards: share of accounts by state</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="percentStacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D32"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$6:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$C$6:$C$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="8BC34A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$6:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$D$6:$D$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!E5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="D9652B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$6:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$E$6:$E$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!F5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9E9E9E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$6:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$F$6:$F$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="0.25"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -750,14 +957,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,585 +973,422 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="33" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>State = income points + liquidity points, then distress. Customer-level signals are read across all accounts of the customer (CIF).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46.5" customHeight="1">
+          <t>Can the customer pay? Income and liquidity give points, payment distress lowers the state, and Unknown marks customers whose money we cannot see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="33" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Internal salary credit, AECB salary, CASA average balance, external card payments, cheque bounces, DDS (direct debit) returns, bureau bounces, customer-initiated CASA transactions. Scope: credit cards and retail loans at 61–180 DPD; 180+ DPD follows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>States</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>In plain words</t>
+          <t>Credit cards and retail loans (Personal Loans, Personal Cash Loans, Auto) at 61–180 DPD. 180+ DPD follows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Customer level</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Salary, CASA, card payments and distress are read across all accounts of the customer (CIF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Principle</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>The state reflects only money we can see. Unknown is absence of data, not evidence of no ability.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>At a glance, 31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>4 points and no distress</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Regular income and a buffer, both confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>≥ 2 but &lt; 4 points and no distress, or 4 points with distress</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>One side confirmed, or both partly; or everything in place but a payment has just failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="33" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>&lt; 2 points with any signal, or &lt; 4 points with distress</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>What we can see shows little or nothing to pay with</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>0 points, no distress, and no CASA with us or a dormant one (no customer-initiated money movement in the window)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>We cannot see the customer's money: absence of data, not evidence of no ability</t>
-        </is>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="11">
+        <f>Results!C6</f>
+        <v/>
+      </c>
+      <c r="B10" s="11">
+        <f>Results!C7</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>Results!C8</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>Results!C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="12">
+        <f>TEXT(Results!B6,"#,##0")&amp;" cards"&amp;IF(Results!E6="",""," · "&amp;TEXT(Results!E6,"#,##0")&amp;" loans")</f>
+        <v/>
+      </c>
+      <c r="B11" s="12">
+        <f>TEXT(Results!B7,"#,##0")&amp;" cards"&amp;IF(Results!E7="",""," · "&amp;TEXT(Results!E7,"#,##0")&amp;" loans")</f>
+        <v/>
+      </c>
+      <c r="C11" s="12">
+        <f>TEXT(Results!B8,"#,##0")&amp;" cards"&amp;IF(Results!E8="",""," · "&amp;TEXT(Results!E8,"#,##0")&amp;" loans")</f>
+        <v/>
+      </c>
+      <c r="D11" s="12">
+        <f>TEXT(Results!B9,"#,##0")&amp;" cards"&amp;IF(Results!E9="",""," · "&amp;TEXT(Results!E9,"#,##0")&amp;" loans")</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Considerations</t>
+          <t>States</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Consideration</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Points</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="46.5" customHeight="1">
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>In plain words</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="33" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Income (internal salary credit, AECB salary)</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>One salary amount per month, the larger of internal and AECB; an AECB salary counts in its extract month and the next. Stable = the window's total ≥ 2 × max(AED 3,000, 2 × the amount due), and the total not more than 25% below the prior window</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="33" customHeight="1">
-      <c r="A16" s="15" t="inlineStr"/>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Some income in the window (AED 1,000 or more in any month) but not Stable: below threshold, irregular or weakening</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="15" t="inlineStr"/>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>No internal salary credit and no AECB salary of AED 1,000 or more in any month of the window</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="46.5" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Liquidity (CASA average balance, external card payments)</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>CASA average balance ≥ max(AED 3,000, 1 × the amount due) in at least 2 of the last 3 months and the 3-month average not more than 50% below the prior 3 months. Or at least one external card payment ≥ max(AED 500, 1 × the amount due) in the last 3 months</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="15" t="inlineStr"/>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Not Adequate, but a CASA average balance of AED 1,000 or more in any of the last 3 months, or any external card payment of that size</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>4 points and no distress</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Regular income and a buffer, both confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46.5" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>2–3 points and no distress, or 4 points with distress</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>One side confirmed, or both partly; or everything in place but a payment just failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>0–1 points, or under 4 points with distress</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>What we can see shows little or nothing to pay with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>0 points, no distress, and no CASA with us or a dormant one</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>We cannot see the customer's money.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="15" t="inlineStr"/>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>No CASA average balance and no external card payment of AED 1,000 or more in the last 3 months</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="46.5" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Distress (cheque bounce, DDS return, bureau bounce)</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>−1 level</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>1 or more cheque bounces, DDS returns or new bureau bounces in the last 3 months</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="33" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Activity gate (CASA transactions)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Dormant</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Income None, Liquidity None, no distress, and no customer-initiated CASA transaction in the last 3 months (no CASA at all included)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Map (every combination has one state)</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr"/>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>State map: income points + liquidity points, then distress</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>No distress</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Liquidity Adequate</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Liquidity Weak</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Liquidity None</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>No distress · Income Stable</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Income Stable</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>No distress · Income Weak</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Income Weak</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>No distress · Income None</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Income None</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>Low (Unknown if the CASA is dormant or absent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>With distress · Income Stable</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Low (Unknown if CASA dormant or absent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>With distress</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Liquidity Adequate</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Liquidity Weak</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Liquidity None</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Income Stable</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>With distress · Income Weak</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Income Weak</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>With distress · Income None</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Income None</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Reading the results</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="33" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>AECB salary alerts arrive only when something changes, so no alert means nothing is known, not that the salary stopped. Pulls every 2 months would give every customer a value and would show a stop as a pull with no salary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="33" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>A customer with fewer alerts in the window than before can look like a fall: 912 accounts reach the window total but fail the 25% check. Some are real falls; the data cannot yet split them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Weak income with nothing else is Low, so a customer with a reported salary can sit below a customer we know nothing about (Unknown).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="33" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>The AECB amount is taken as accurate on the pull date. It rarely equals the internal salary where both exist, and what it looks back over is not yet known.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>August is the lowest month for Moderate. The alert data used ends on 27 August, so the month is slightly short.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Internal salary and balances cover the PRB, PSB and PB segments (95% of base customers). Internal salary history starts in September 2024.</t>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rules: 'Logic'. Which rule gave each state: 'Results detail'. What we can see of the customer: 'Results summaries'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B26:C26"/>
+  <mergeCells count="10">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1353,6 +1396,404 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="33" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>What the model computes for each account at the end of the scoring month. The window is the scoring month and the 2 before it; the prior window is the 3 months before that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46.5" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Income: Stable</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>One salary amount per month. The window's total at least 2 × the threshold, and no more than 25% below the prior window. Threshold = max(AED 3,000, 2 × the amount due).</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>2 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Income: Weak</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Not Stable, but AED 1,000 or more in any month of the window.</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>1 point</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Income: None</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Nothing of AED 1,000 or more in the window.</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>0 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46.5" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Liquidity: Adequate</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>CASA average balance at least max(AED 3,000, the amount due) in 2 of 3 months and no more than 50% below the prior window; or an external card payment of at least max(AED 500, the amount due).</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>2 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Liquidity: Weak</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Not Adequate, but a balance or card payment of AED 1,000 or more.</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>1 point</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Liquidity: None</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Neither.</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>0 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Distress</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>A cheque bounce, DDS return or new bureau bounce in the window.</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Down one level</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Activity gate</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>0 points, no distress and no customer money movement in the window.</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Unknown instead of Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Salary per month</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>Internal salary</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>The month's salary-flagged credits with us, bonuses included.</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>The month of the credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>AECB salary</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>The reported average salary on a salary alert (average salary changed, salary account added), accurate on the pull date.</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>The pull's month and the next one, never earlier and no later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Salary account closed</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>An AECB closure alert ends the AECB salary.</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>From the alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>One amount per month</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>The larger of internal and AECB, never the sum.</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Each month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Distress</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Cheque / DDS return</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>A returned cheque or direct debit on any CASA of the customer.</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>The month of the return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Bureau bounce</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>A new bounced amount on a pull; repeated unchanged it counts once.</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>The pull's month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Customer money movement (the activity gate)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="13" t="inlineStr"/>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Transactions</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Transfers in and out, remittances, cash, clearing, bill payments, card spend, paying their own credit card.</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr"/>
+    </row>
+    <row r="30" ht="33" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Does not count</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>The bank recovering the customer's loan instalment, transfers between their own accounts, fees, interest, reversals.</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F3864"/>
@@ -1381,204 +1822,204 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Window (the scoring month included), 61–180 DPD / 180+ DPD</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>3 / 6 months</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Months of the window at the CASA floor</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>2 of 3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Salary floor, internal and AECB</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>AED 3,000</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Income: multiple of the amount due</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Stable: window total, multiples of the income threshold (3 at 180+)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Income weakening: fall of the window total vs the prior window</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>AECB salary: months counted after the extract month</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>CASA average balance floor</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>AED 3,000</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>CASA: multiple of the amount due</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>CASA weakening: fall of the average vs the prior window</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>External card payment floor</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>AED 500</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>External card payment: multiple of the amount due</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Smallest amount that counts as evidence</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>AED 1,000</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Distress events in the window that count</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Points needed for High / Moderate</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>4 / 2</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>CASA held: months of history for a leg or positive balance</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1595,242 +2036,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A22:B22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F3864"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>How the inputs are read. The window is the scoring month and the 2 before it; the prior window is the 3 months before that.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Salary per month</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Internal salary</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>The month's salary-flagged credits with us, bonuses included.</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>The month of the credit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>AECB salary</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>The reported average salary on a salary alert (average salary changed, salary account added), accurate on the pull date.</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>The pull's month and the next one, never earlier and no later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Salary account closed</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>An AECB closure alert ends the AECB salary.</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>From the alert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>One amount per month</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>The larger of internal and AECB, never the sum.</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Each month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Distress</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Cheque / DDS return</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>A returned cheque or direct debit on any CASA of the customer.</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>The month of the return.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Bureau bounce</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>A new bounced amount on a pull; repeated unchanged it counts once.</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>The pull's month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Customer money movement (the activity gate)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="7" t="inlineStr"/>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Transactions</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="33" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Transfers in and out, remittances, cash, clearing, bill payments, card spend, paying their own credit card.</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Does not count</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>The bank recovering the customer's loan instalment, transfers between their own accounts, fees, interest, reversals.</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1886,491 +2091,491 @@
       <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Cells</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>5,000  internal salary</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>A 3,000  AECB pull</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>→ carried</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>× closed</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>Two salaries with us, 10,000 against 6,000.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="28" t="n"/>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>Employer paid two salaries in one month: the total counts.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Three salaries of 2,000 reach the 6,000 total.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>A 3,000</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>→ 3,000</t>
         </is>
       </c>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>AECB pull in the window's first month: counts for 2 months.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>A 6,000</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>AECB pull this month: one month, but 6,000 reaches the total.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>A 3,000</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>→ 3,000</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>A 3,000</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>Pulls every 2 months fill the window.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>A 6,000</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>→ 6,000</t>
         </is>
       </c>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Pull just before the window carries into its first month.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>A 3,000</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>AECB pull this month at 3,000: one month, 3,000 against 6,000.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>1,200</t>
         </is>
       </c>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Salary, but 5,200 against the 6,000 total.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>AED 3,000 overdue lifts the total needed to 12,000.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="33" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n"/>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>A 10,000</t>
         </is>
       </c>
-      <c r="G17" s="30" t="inlineStr">
+      <c r="G17" s="31" t="inlineStr">
         <is>
           <t>→ 10,000</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Salary with us stopped; one AECB pull gives 20,000 against 30,000: more than 25% below.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>A 7,000</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="31" t="inlineStr">
         <is>
           <t>→ 7,000</t>
         </is>
       </c>
-      <c r="E18" s="28" t="n"/>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>A 4,000</t>
         </is>
       </c>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="G18" s="31" t="inlineStr">
         <is>
           <t>→ 4,000</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>AECB level fell: 8,000 against 14,000.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>A 3,000</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G19" s="28" t="n"/>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Salary account closed: the AECB amount does not carry.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>Below AED 1,000.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>A 9,000</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>→ 9,000</t>
         </is>
       </c>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="29" t="n"/>
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>AECB pull and its carry are both before the window.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>No salary from either source.</t>
         </is>
@@ -2391,340 +2596,340 @@
       <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Liquidity</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Distress</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Customer money movement</t>
         </is>
       </c>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>Adequate</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>Salary and balance both confirmed.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>AECB salary, nothing with us.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>Adequate</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>No salary seen, but paying an external card.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>Adequate</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>Everything in place, but a payment just failed.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>Some reported income, nothing else.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>Uses the account, but money does not stay.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>Stable income, but a cheque bounced.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>A bureau bounce is all we see.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>No CASA with us, or a dormant one: we cannot see their money.</t>
         </is>
@@ -2776,7 +2981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2824,226 +3029,291 @@
       <c r="K4" s="6" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Personal Loans</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Personal Cash Loans</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="K5" s="9" t="n"/>
+      <c r="K5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>IF(OR(B6="",N(B$10)=0),"",B6/B$10)</f>
         <v/>
       </c>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="32">
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="33">
         <f>IF(OR(D6="",N(D$10)=0),"",D6/D$10)</f>
         <v/>
       </c>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="32">
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="33">
         <f>IF(OR(F6="",N(F$10)=0),"",F6/F$10)</f>
         <v/>
       </c>
-      <c r="H6" s="31" t="n"/>
-      <c r="I6" s="32">
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="33">
         <f>IF(OR(H6="",N(H$10)=0),"",H6/H$10)</f>
         <v/>
       </c>
-      <c r="J6" s="31" t="n"/>
-      <c r="K6" s="32">
+      <c r="J6" s="32" t="n"/>
+      <c r="K6" s="33">
         <f>IF(OR(J6="",N(J$10)=0),"",J6/J$10)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>2689</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>IF(OR(B7="",N(B$10)=0),"",B7/B$10)</f>
         <v/>
       </c>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="32">
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="33">
         <f>IF(OR(D7="",N(D$10)=0),"",D7/D$10)</f>
         <v/>
       </c>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="32">
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33">
         <f>IF(OR(F7="",N(F$10)=0),"",F7/F$10)</f>
         <v/>
       </c>
-      <c r="H7" s="31" t="n"/>
-      <c r="I7" s="32">
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="33">
         <f>IF(OR(H7="",N(H$10)=0),"",H7/H$10)</f>
         <v/>
       </c>
-      <c r="J7" s="31" t="n"/>
-      <c r="K7" s="32">
+      <c r="J7" s="32" t="n"/>
+      <c r="K7" s="33">
         <f>IF(OR(J7="",N(J$10)=0),"",J7/J$10)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>5737</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>IF(OR(B8="",N(B$10)=0),"",B8/B$10)</f>
         <v/>
       </c>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="32">
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="33">
         <f>IF(OR(D8="",N(D$10)=0),"",D8/D$10)</f>
         <v/>
       </c>
-      <c r="F8" s="31" t="n"/>
-      <c r="G8" s="32">
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33">
         <f>IF(OR(F8="",N(F$10)=0),"",F8/F$10)</f>
         <v/>
       </c>
-      <c r="H8" s="31" t="n"/>
-      <c r="I8" s="32">
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="33">
         <f>IF(OR(H8="",N(H$10)=0),"",H8/H$10)</f>
         <v/>
       </c>
-      <c r="J8" s="31" t="n"/>
-      <c r="K8" s="32">
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="33">
         <f>IF(OR(J8="",N(J$10)=0),"",J8/J$10)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>10819</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>IF(OR(B9="",N(B$10)=0),"",B9/B$10)</f>
         <v/>
       </c>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="32">
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="33">
         <f>IF(OR(D9="",N(D$10)=0),"",D9/D$10)</f>
         <v/>
       </c>
-      <c r="F9" s="31" t="n"/>
-      <c r="G9" s="32">
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33">
         <f>IF(OR(F9="",N(F$10)=0),"",F9/F$10)</f>
         <v/>
       </c>
-      <c r="H9" s="31" t="n"/>
-      <c r="I9" s="32">
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="33">
         <f>IF(OR(H9="",N(H$10)=0),"",H9/H$10)</f>
         <v/>
       </c>
-      <c r="J9" s="31" t="n"/>
-      <c r="K9" s="32">
+      <c r="J9" s="32" t="n"/>
+      <c r="K9" s="33">
         <f>IF(OR(J9="",N(J$10)=0),"",J9/J$10)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>IF(COUNT(B6:B9)=0,"",SUM(B6:B9))</f>
         <v/>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="34">
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="35">
         <f>IF(COUNT(D6:D9)=0,"",SUM(D6:D9))</f>
         <v/>
       </c>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="34">
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="35">
         <f>IF(COUNT(F6:F9)=0,"",SUM(F6:F9))</f>
         <v/>
       </c>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="34">
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="35">
         <f>IF(COUNT(H6:H9)=0,"",SUM(H6:H9))</f>
         <v/>
       </c>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="34">
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="35">
         <f>IF(COUNT(J6:J9)=0,"",SUM(J6:J9))</f>
         <v/>
       </c>
-      <c r="K10" s="35" t="n"/>
-    </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="K10" s="36" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Reading the results</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="33" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AECB salary alerts arrive only when something changes, so no alert means nothing is known, not that the salary stopped. Pulls every 2 months would give every customer a value and would show a stop as a pull with no salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>A customer with fewer alerts in the window than before can look like a fall: 912 accounts reach the window total but fail the 25% check. Some are real falls; the data cannot yet split them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Weak income with nothing else is Low, so a customer with a reported salary can sit below a customer we know nothing about (Unknown).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="33" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The AECB amount is taken as accurate on the pull date. It rarely equals the internal salary where both exist, and what it looks back over is not yet known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>August is the lowest month for Moderate. The alert data used ends on 27 August, so the month is slightly short.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Internal salary and balances cover the PRB, PSB and PB segments (95% of base customers). Internal salary history starts in September 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Which rule gave each state: 'Results detail'. Coverage of salary, CASA and bureau: 'Results summaries'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A15:K15"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A19:K19"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3093,170 +3363,170 @@
       <c r="E4" s="6" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr"/>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Accounts</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>19292</v>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="35" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="36" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Stable · internal salary only</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>190</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>IF(OR(B7="",N(B$6)=0),"",B7/B$6)</f>
         <v/>
       </c>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="32">
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="33">
         <f>IF(OR(D7="",N(D$6)=0),"",D7/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Stable · AECB salary only</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>2656</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>IF(OR(B8="",N(B$6)=0),"",B8/B$6)</f>
         <v/>
       </c>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="32">
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="33">
         <f>IF(OR(D8="",N(D$6)=0),"",D8/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Stable · both</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>IF(OR(B9="",N(B$6)=0),"",B9/B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="32">
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="33">
         <f>IF(OR(D9="",N(D$6)=0),"",D9/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Weak · internal salary only</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>212</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>IF(OR(B10="",N(B$6)=0),"",B10/B$6)</f>
         <v/>
       </c>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="32">
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="33">
         <f>IF(OR(D10="",N(D$6)=0),"",D10/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Weak · AECB salary only</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>1807</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>IF(OR(B11="",N(B$6)=0),"",B11/B$6)</f>
         <v/>
       </c>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="32">
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="33">
         <f>IF(OR(D11="",N(D$6)=0),"",D11/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Weak · both</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>IF(OR(B12="",N(B$6)=0),"",B12/B$6)</f>
         <v/>
       </c>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="32">
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="33">
         <f>IF(OR(D12="",N(D$6)=0),"",D12/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>None · no salary of AED 1,000 or more in the window</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <v>14389</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>IF(OR(B13="",N(B$6)=0),"",B13/B$6)</f>
         <v/>
       </c>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="32">
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="33">
         <f>IF(OR(D13="",N(D$6)=0),"",D13/D$6)</f>
         <v/>
       </c>
@@ -3273,119 +3543,119 @@
       <c r="E15" s="6" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="inlineStr"/>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Stable · 1 AECB month in the window</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>292</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>IF(OR(B17="",N(B$6)=0),"",B17/B$6)</f>
         <v/>
       </c>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="32">
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="33">
         <f>IF(OR(D17="",N(D$6)=0),"",D17/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Stable · 2 AECB months</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="32" t="n">
         <v>1225</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <f>IF(OR(B18="",N(B$6)=0),"",B18/B$6)</f>
         <v/>
       </c>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="32">
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="33">
         <f>IF(OR(D18="",N(D$6)=0),"",D18/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Stable · 3 AECB months</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="32" t="n">
         <v>1165</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="33">
         <f>IF(OR(B19="",N(B$6)=0),"",B19/B$6)</f>
         <v/>
       </c>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="32">
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="33">
         <f>IF(OR(D19="",N(D$6)=0),"",D19/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Weak · window total reached, but more than 25% below the prior window</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="32" t="n">
         <v>912</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="33">
         <f>IF(OR(B20="",N(B$6)=0),"",B20/B$6)</f>
         <v/>
       </c>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="32">
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="33">
         <f>IF(OR(D20="",N(D$6)=0),"",D20/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Weak · window total not reached</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="32" t="n">
         <v>907</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <f>IF(OR(B21="",N(B$6)=0),"",B21/B$6)</f>
         <v/>
       </c>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="32">
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="33">
         <f>IF(OR(D21="",N(D$6)=0),"",D21/D$6)</f>
         <v/>
       </c>
@@ -3402,138 +3672,138 @@
       <c r="E23" s="6" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="7" t="inlineStr"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr"/>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Adequate · CASA balance (no external card payment)</t>
         </is>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <v>142</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <f>IF(OR(B25="",N(B$6)=0),"",B25/B$6)</f>
         <v/>
       </c>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="32">
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="33">
         <f>IF(OR(D25="",N(D$6)=0),"",D25/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Adequate · with an external card payment (card or CASA arm)</t>
         </is>
       </c>
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <v>54</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="33">
         <f>IF(OR(B26="",N(B$6)=0),"",B26/B$6)</f>
         <v/>
       </c>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="32">
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="33">
         <f>IF(OR(D26="",N(D$6)=0),"",D26/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Weak · CASA balance of AED 1,000 or more (no card payment)</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="32" t="n">
         <v>327</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <f>IF(OR(B27="",N(B$6)=0),"",B27/B$6)</f>
         <v/>
       </c>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="32">
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="33">
         <f>IF(OR(D27="",N(D$6)=0),"",D27/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Weak · with an external card payment</t>
         </is>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <f>IF(OR(B28="",N(B$6)=0),"",B28/B$6)</f>
         <v/>
       </c>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="32">
+      <c r="D28" s="32" t="n"/>
+      <c r="E28" s="33">
         <f>IF(OR(D28="",N(D$6)=0),"",D28/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>None · a card payment below AED 1,000</t>
         </is>
       </c>
-      <c r="B29" s="31" t="n">
+      <c r="B29" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="33">
         <f>IF(OR(B29="",N(B$6)=0),"",B29/B$6)</f>
         <v/>
       </c>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="32">
+      <c r="D29" s="32" t="n"/>
+      <c r="E29" s="33">
         <f>IF(OR(D29="",N(D$6)=0),"",D29/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>None · no CASA balance or card payment</t>
         </is>
       </c>
-      <c r="B30" s="31" t="n">
+      <c r="B30" s="32" t="n">
         <v>18705</v>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="33">
         <f>IF(OR(B30="",N(B$6)=0),"",B30/B$6)</f>
         <v/>
       </c>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="32">
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="33">
         <f>IF(OR(D30="",N(D$6)=0),"",D30/D$6)</f>
         <v/>
       </c>
@@ -3550,119 +3820,119 @@
       <c r="E32" s="6" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="7" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr"/>
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>No distress</t>
         </is>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <v>17616</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <f>IF(OR(B34="",N(B$6)=0),"",B34/B$6)</f>
         <v/>
       </c>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="32">
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="33">
         <f>IF(OR(D34="",N(D$6)=0),"",D34/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Bureau bounce only</t>
         </is>
       </c>
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="32" t="n">
         <v>483</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="33">
         <f>IF(OR(B35="",N(B$6)=0),"",B35/B$6)</f>
         <v/>
       </c>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="32">
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="33">
         <f>IF(OR(D35="",N(D$6)=0),"",D35/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Cheque return only</t>
         </is>
       </c>
-      <c r="B36" s="31" t="n">
+      <c r="B36" s="32" t="n">
         <v>451</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <f>IF(OR(B36="",N(B$6)=0),"",B36/B$6)</f>
         <v/>
       </c>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="32">
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="33">
         <f>IF(OR(D36="",N(D$6)=0),"",D36/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Direct-debit return only</t>
         </is>
       </c>
-      <c r="B37" s="31" t="n">
+      <c r="B37" s="32" t="n">
         <v>596</v>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="33">
         <f>IF(OR(B37="",N(B$6)=0),"",B37/B$6)</f>
         <v/>
       </c>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="32">
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="33">
         <f>IF(OR(D37="",N(D$6)=0),"",D37/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Two or more kinds</t>
         </is>
       </c>
-      <c r="B38" s="31" t="n">
+      <c r="B38" s="32" t="n">
         <v>146</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <f>IF(OR(B38="",N(B$6)=0),"",B38/B$6)</f>
         <v/>
       </c>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="32">
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="33">
         <f>IF(OR(D38="",N(D$6)=0),"",D38/D$6)</f>
         <v/>
       </c>
@@ -3679,157 +3949,157 @@
       <c r="E40" s="6" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="7" t="inlineStr"/>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>High · Stable income, Adequate liquidity</t>
         </is>
       </c>
-      <c r="B42" s="31" t="n">
+      <c r="B42" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <f>IF(OR(B42="",N(B$6)=0),"",B42/B$6)</f>
         <v/>
       </c>
-      <c r="D42" s="31" t="n"/>
-      <c r="E42" s="32">
+      <c r="D42" s="32" t="n"/>
+      <c r="E42" s="33">
         <f>IF(OR(D42="",N(D$6)=0),"",D42/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>Moderate · Stable income, no liquidity</t>
         </is>
       </c>
-      <c r="B43" s="31" t="n">
+      <c r="B43" s="32" t="n">
         <v>2492</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="33">
         <f>IF(OR(B43="",N(B$6)=0),"",B43/B$6)</f>
         <v/>
       </c>
-      <c r="D43" s="31" t="n"/>
-      <c r="E43" s="32">
+      <c r="D43" s="32" t="n"/>
+      <c r="E43" s="33">
         <f>IF(OR(D43="",N(D$6)=0),"",D43/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Moderate · no income, Adequate liquidity</t>
         </is>
       </c>
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="32" t="n">
         <v>89</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <f>IF(OR(B44="",N(B$6)=0),"",B44/B$6)</f>
         <v/>
       </c>
-      <c r="D44" s="31" t="n"/>
-      <c r="E44" s="32">
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="33">
         <f>IF(OR(D44="",N(D$6)=0),"",D44/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>Moderate · Stable income, Weak liquidity</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <f>IF(OR(B45="",N(B$6)=0),"",B45/B$6)</f>
         <v/>
       </c>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32">
+      <c r="D45" s="32" t="n"/>
+      <c r="E45" s="33">
         <f>IF(OR(D45="",N(D$6)=0),"",D45/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Moderate · Weak income, Weak liquidity</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="33">
         <f>IF(OR(B46="",N(B$6)=0),"",B46/B$6)</f>
         <v/>
       </c>
-      <c r="D46" s="31" t="n"/>
-      <c r="E46" s="32">
+      <c r="D46" s="32" t="n"/>
+      <c r="E46" s="33">
         <f>IF(OR(D46="",N(D$6)=0),"",D46/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Moderate · Weak income, Adequate liquidity</t>
         </is>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="33">
         <f>IF(OR(B47="",N(B$6)=0),"",B47/B$6)</f>
         <v/>
       </c>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32">
+      <c r="D47" s="32" t="n"/>
+      <c r="E47" s="33">
         <f>IF(OR(D47="",N(D$6)=0),"",D47/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Moderate · 4 points with distress</t>
         </is>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <f>IF(OR(B48="",N(B$6)=0),"",B48/B$6)</f>
         <v/>
       </c>
-      <c r="D48" s="31" t="n"/>
-      <c r="E48" s="32">
+      <c r="D48" s="32" t="n"/>
+      <c r="E48" s="33">
         <f>IF(OR(D48="",N(D$6)=0),"",D48/D$6)</f>
         <v/>
       </c>
@@ -3846,100 +4116,100 @@
       <c r="E50" s="6" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="7" t="inlineStr"/>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr"/>
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>1 point (mostly Weak income, nothing else)</t>
         </is>
       </c>
-      <c r="B52" s="31" t="n">
+      <c r="B52" s="32" t="n">
         <v>2211</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="33">
         <f>IF(OR(B52="",N(B$6)=0),"",B52/B$6)</f>
         <v/>
       </c>
-      <c r="D52" s="31" t="n"/>
-      <c r="E52" s="32">
+      <c r="D52" s="32" t="n"/>
+      <c r="E52" s="33">
         <f>IF(OR(D52="",N(D$6)=0),"",D52/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>0 points, an active CASA where money does not stay</t>
         </is>
       </c>
-      <c r="B53" s="31" t="n">
+      <c r="B53" s="32" t="n">
         <v>2065</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <f>IF(OR(B53="",N(B$6)=0),"",B53/B$6)</f>
         <v/>
       </c>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="32">
+      <c r="D53" s="32" t="n"/>
+      <c r="E53" s="33">
         <f>IF(OR(D53="",N(D$6)=0),"",D53/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>0 points with distress</t>
         </is>
       </c>
-      <c r="B54" s="31" t="n">
+      <c r="B54" s="32" t="n">
         <v>1151</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="33">
         <f>IF(OR(B54="",N(B$6)=0),"",B54/B$6)</f>
         <v/>
       </c>
-      <c r="D54" s="31" t="n"/>
-      <c r="E54" s="32">
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="33">
         <f>IF(OR(D54="",N(D$6)=0),"",D54/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>2–3 points with distress</t>
         </is>
       </c>
-      <c r="B55" s="31" t="n">
+      <c r="B55" s="32" t="n">
         <v>310</v>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="33">
         <f>IF(OR(B55="",N(B$6)=0),"",B55/B$6)</f>
         <v/>
       </c>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="32">
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="33">
         <f>IF(OR(D55="",N(D$6)=0),"",D55/D$6)</f>
         <v/>
       </c>
@@ -3956,62 +4226,62 @@
       <c r="E57" s="6" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="7" t="inlineStr"/>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr"/>
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Dormant CASA: no customer money movement in the window</t>
         </is>
       </c>
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="32" t="n">
         <v>6744</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <f>IF(OR(B59="",N(B$6)=0),"",B59/B$6)</f>
         <v/>
       </c>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="32">
+      <c r="D59" s="32" t="n"/>
+      <c r="E59" s="33">
         <f>IF(OR(D59="",N(D$6)=0),"",D59/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>No CASA with us (no transaction or positive balance in 12 months)</t>
         </is>
       </c>
-      <c r="B60" s="31" t="n">
+      <c r="B60" s="32" t="n">
         <v>4075</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="33">
         <f>IF(OR(B60="",N(B$6)=0),"",B60/B$6)</f>
         <v/>
       </c>
-      <c r="D60" s="31" t="n"/>
-      <c r="E60" s="32">
+      <c r="D60" s="32" t="n"/>
+      <c r="E60" s="33">
         <f>IF(OR(D60="",N(D$6)=0),"",D60/D$6)</f>
         <v/>
       </c>
@@ -4028,6 +4298,132 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A62:E62"/>
   </mergeCells>
+  <conditionalFormatting sqref="C7:C13">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E13">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:C21">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E21">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:C30">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:E30">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C34:C38">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34:E38">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C42:C48">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42:E48">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C52:C55">
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E52:E55">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C59:C60">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E59:E60">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4076,94 +4472,94 @@
       <c r="E4" s="6" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr"/>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Accounts</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>19292</v>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="35" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="36" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Active: customer moved money in the window</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>3631</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>IF(OR(B7="",N(B$6)=0),"",B7/B$6)</f>
         <v/>
       </c>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="32">
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="33">
         <f>IF(OR(D7="",N(D$6)=0),"",D7/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Dormant: holds a CASA, no customer movement</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>9125</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>IF(OR(B8="",N(B$6)=0),"",B8/B$6)</f>
         <v/>
       </c>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="32">
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="33">
         <f>IF(OR(D8="",N(D$6)=0),"",D8/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>No CASA with us</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>6536</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>IF(OR(B9="",N(B$6)=0),"",B9/B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="32">
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="33">
         <f>IF(OR(D9="",N(D$6)=0),"",D9/D$6)</f>
         <v/>
       </c>
@@ -4180,119 +4576,119 @@
       <c r="E11" s="6" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr"/>
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>In the window</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <v>440</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>IF(OR(B13="",N(B$6)=0),"",B13/B$6)</f>
         <v/>
       </c>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="32">
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="33">
         <f>IF(OR(D13="",N(D$6)=0),"",D13/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>4–6 months ago</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>3094</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>IF(OR(B14="",N(B$6)=0),"",B14/B$6)</f>
         <v/>
       </c>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="32">
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="33">
         <f>IF(OR(D14="",N(D$6)=0),"",D14/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>7–12 months ago</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="32" t="n">
         <v>3599</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="33">
         <f>IF(OR(B15="",N(B$6)=0),"",B15/B$6)</f>
         <v/>
       </c>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="32">
+      <c r="D15" s="32" t="n"/>
+      <c r="E15" s="33">
         <f>IF(OR(D15="",N(D$6)=0),"",D15/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>13–24 months ago</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="32" t="n">
         <v>1941</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>IF(OR(B16="",N(B$6)=0),"",B16/B$6)</f>
         <v/>
       </c>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="32">
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="33">
         <f>IF(OR(D16="",N(D$6)=0),"",D16/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>No salary in 24 months (the history available)</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>10218</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>IF(OR(B17="",N(B$6)=0),"",B17/B$6)</f>
         <v/>
       </c>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="32">
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="33">
         <f>IF(OR(D17="",N(D$6)=0),"",D17/D$6)</f>
         <v/>
       </c>
@@ -4309,157 +4705,157 @@
       <c r="E19" s="6" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="7" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>In the window</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="32" t="n">
         <v>3729</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <f>IF(OR(B21="",N(B$6)=0),"",B21/B$6)</f>
         <v/>
       </c>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="32">
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="33">
         <f>IF(OR(D21="",N(D$6)=0),"",D21/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>4–6 months ago</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <v>2362</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <f>IF(OR(B22="",N(B$6)=0),"",B22/B$6)</f>
         <v/>
       </c>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="32">
+      <c r="D22" s="32" t="n"/>
+      <c r="E22" s="33">
         <f>IF(OR(D22="",N(D$6)=0),"",D22/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>7–12 months ago</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="32" t="n">
         <v>2097</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="33">
         <f>IF(OR(B23="",N(B$6)=0),"",B23/B$6)</f>
         <v/>
       </c>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="32">
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="33">
         <f>IF(OR(D23="",N(D$6)=0),"",D23/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>13–24 months ago</t>
         </is>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <v>1349</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <f>IF(OR(B24="",N(B$6)=0),"",B24/B$6)</f>
         <v/>
       </c>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="32">
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="33">
         <f>IF(OR(D24="",N(D$6)=0),"",D24/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>25 or more months ago</t>
         </is>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <v>902</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <f>IF(OR(B25="",N(B$6)=0),"",B25/B$6)</f>
         <v/>
       </c>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="32">
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="33">
         <f>IF(OR(D25="",N(D$6)=0),"",D25/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Alert rows, never a salary</t>
         </is>
       </c>
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <v>7644</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="33">
         <f>IF(OR(B26="",N(B$6)=0),"",B26/B$6)</f>
         <v/>
       </c>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="32">
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="33">
         <f>IF(OR(D26="",N(D$6)=0),"",D26/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>No alert row</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="32" t="n">
         <v>1209</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <f>IF(OR(B27="",N(B$6)=0),"",B27/B$6)</f>
         <v/>
       </c>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="32">
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="33">
         <f>IF(OR(D27="",N(D$6)=0),"",D27/D$6)</f>
         <v/>
       </c>
@@ -4476,81 +4872,81 @@
       <c r="E29" s="6" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="7" t="inlineStr"/>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr"/>
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>In the window</t>
         </is>
       </c>
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="32" t="n">
         <v>4135</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <f>IF(OR(B31="",N(B$6)=0),"",B31/B$6)</f>
         <v/>
       </c>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="32">
+      <c r="D31" s="32" t="n"/>
+      <c r="E31" s="33">
         <f>IF(OR(D31="",N(D$6)=0),"",D31/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Only older</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="32" t="n">
         <v>12332</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="33">
         <f>IF(OR(B32="",N(B$6)=0),"",B32/B$6)</f>
         <v/>
       </c>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="32">
+      <c r="D32" s="32" t="n"/>
+      <c r="E32" s="33">
         <f>IF(OR(D32="",N(D$6)=0),"",D32/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>None: no internal salary in 24 months, no AECB salary alert</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="32" t="n">
         <v>2825</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <f>IF(OR(B33="",N(B$6)=0),"",B33/B$6)</f>
         <v/>
       </c>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="32">
+      <c r="D33" s="32" t="n"/>
+      <c r="E33" s="33">
         <f>IF(OR(D33="",N(D$6)=0),"",D33/D$6)</f>
         <v/>
       </c>
@@ -4567,100 +4963,100 @@
       <c r="E35" s="6" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="7" t="inlineStr"/>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr"/>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Stopped · no income in the window</t>
         </is>
       </c>
-      <c r="B37" s="31" t="n">
+      <c r="B37" s="32" t="n">
         <v>2679</v>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="33">
         <f>IF(OR(B37="",N(B$6)=0),"",B37/B$6)</f>
         <v/>
       </c>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="32">
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="33">
         <f>IF(OR(D37="",N(D$6)=0),"",D37/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Stopped · Weak on AECB salary</t>
         </is>
       </c>
-      <c r="B38" s="31" t="n">
+      <c r="B38" s="32" t="n">
         <v>208</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <f>IF(OR(B38="",N(B$6)=0),"",B38/B$6)</f>
         <v/>
       </c>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="32">
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="33">
         <f>IF(OR(D38="",N(D$6)=0),"",D38/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Stopped · Stable on AECB salary</t>
         </is>
       </c>
-      <c r="B39" s="31" t="n">
+      <c r="B39" s="32" t="n">
         <v>207</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <f>IF(OR(B39="",N(B$6)=0),"",B39/B$6)</f>
         <v/>
       </c>
-      <c r="D39" s="31" t="n"/>
-      <c r="E39" s="32">
+      <c r="D39" s="32" t="n"/>
+      <c r="E39" s="33">
         <f>IF(OR(D39="",N(D$6)=0),"",D39/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Not stopped</t>
         </is>
       </c>
-      <c r="B40" s="31" t="n">
+      <c r="B40" s="32" t="n">
         <v>16198</v>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="33">
         <f>IF(OR(B40="",N(B$6)=0),"",B40/B$6)</f>
         <v/>
       </c>
-      <c r="D40" s="31" t="n"/>
-      <c r="E40" s="32">
+      <c r="D40" s="32" t="n"/>
+      <c r="E40" s="33">
         <f>IF(OR(D40="",N(D$6)=0),"",D40/D$6)</f>
         <v/>
       </c>
@@ -4677,100 +5073,100 @@
       <c r="E42" s="6" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="7" t="inlineStr"/>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr"/>
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>AED 3,000 or more</t>
         </is>
       </c>
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="32" t="n">
         <v>242</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <f>IF(OR(B44="",N(B$6)=0),"",B44/B$6)</f>
         <v/>
       </c>
-      <c r="D44" s="31" t="n"/>
-      <c r="E44" s="32">
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="33">
         <f>IF(OR(D44="",N(D$6)=0),"",D44/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>AED 1,000–3,000</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="32" t="n">
         <v>254</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <f>IF(OR(B45="",N(B$6)=0),"",B45/B$6)</f>
         <v/>
       </c>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32">
+      <c r="D45" s="32" t="n"/>
+      <c r="E45" s="33">
         <f>IF(OR(D45="",N(D$6)=0),"",D45/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Under AED 1,000</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="32" t="n">
         <v>4775</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="33">
         <f>IF(OR(B46="",N(B$6)=0),"",B46/B$6)</f>
         <v/>
       </c>
-      <c r="D46" s="31" t="n"/>
-      <c r="E46" s="32">
+      <c r="D46" s="32" t="n"/>
+      <c r="E46" s="33">
         <f>IF(OR(D46="",N(D$6)=0),"",D46/D$6)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>No balance</t>
         </is>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="32" t="n">
         <v>14021</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="33">
         <f>IF(OR(B47="",N(B$6)=0),"",B47/B$6)</f>
         <v/>
       </c>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32">
+      <c r="D47" s="32" t="n"/>
+      <c r="E47" s="33">
         <f>IF(OR(D47="",N(D$6)=0),"",D47/D$6)</f>
         <v/>
       </c>
@@ -4787,43 +5183,43 @@
       <c r="E49" s="6" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="7" t="inlineStr"/>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr"/>
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>Retail loans</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B51" s="31" t="n">
+      <c r="B51" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <f>IF(OR(B51="",N(B$6)=0),"",B51/B$6)</f>
         <v/>
       </c>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="32">
+      <c r="D51" s="32" t="n"/>
+      <c r="E51" s="33">
         <f>IF(OR(D51="",N(D$6)=0),"",D51/D$6)</f>
         <v/>
       </c>
@@ -4851,6 +5247,132 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A54:E54"/>
   </mergeCells>
+  <conditionalFormatting sqref="C7:C9">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E9">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:C17">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E17">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:C27">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E27">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31:C33">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E33">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:C40">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:E40">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C44:C47">
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E44:E47">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C51">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E51">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="009DC3E6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4889,140 +5411,140 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr"/>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>AECB in window</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>AECB 4–6 m</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>AECB 7–12 m</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>AECB 13+ m</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Internal in window</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="32" t="n">
         <v>79</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="32" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Internal 4–6 m</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>349</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="32" t="n">
         <v>121</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="32" t="n">
         <v>88</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="32" t="n">
         <v>299</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="32" t="n">
         <v>2237</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Internal 7–12 m</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>438</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="32" t="n">
         <v>265</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="32" t="n">
         <v>197</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="32" t="n">
         <v>310</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="32" t="n">
         <v>2389</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Internal 13–24 m</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>268</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="32" t="n">
         <v>167</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="32" t="n">
         <v>189</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="32" t="n">
         <v>213</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="32" t="n">
         <v>1104</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>No internal in 24 m</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>2640</v>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="32" t="n">
         <v>1794</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="32" t="n">
         <v>1609</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="32" t="n">
         <v>1350</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="32" t="n">
         <v>2825</v>
       </c>
     </row>
@@ -5088,44 +5610,44 @@
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Accounts</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>14664</v>
       </c>
       <c r="C6" s="37" t="n">
@@ -5142,12 +5664,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>14576</v>
       </c>
       <c r="C7" s="37" t="n">
@@ -5164,12 +5686,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>14455</v>
       </c>
       <c r="C8" s="37" t="n">
@@ -5186,12 +5708,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Apr 2026</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>14671</v>
       </c>
       <c r="C9" s="37" t="n">
@@ -5208,12 +5730,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>15890</v>
       </c>
       <c r="C10" s="37" t="n">
@@ -5230,12 +5752,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>16982</v>
       </c>
       <c r="C11" s="37" t="n">
@@ -5252,12 +5774,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <v>18397</v>
       </c>
       <c r="C12" s="37" t="n">
@@ -5274,12 +5796,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <v>19292</v>
       </c>
       <c r="C13" s="37" t="n">
@@ -5308,128 +5830,128 @@
       <c r="F15" s="6" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Accounts</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F16" s="36" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
+      <c r="B17" s="32" t="n"/>
       <c r="C17" s="37" t="n"/>
       <c r="D17" s="37" t="n"/>
       <c r="E17" s="37" t="n"/>
       <c r="F17" s="37" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
+      <c r="B18" s="32" t="n"/>
       <c r="C18" s="37" t="n"/>
       <c r="D18" s="37" t="n"/>
       <c r="E18" s="37" t="n"/>
       <c r="F18" s="37" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n"/>
+      <c r="B19" s="32" t="n"/>
       <c r="C19" s="37" t="n"/>
       <c r="D19" s="37" t="n"/>
       <c r="E19" s="37" t="n"/>
       <c r="F19" s="37" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Apr 2026</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
       <c r="C20" s="37" t="n"/>
       <c r="D20" s="37" t="n"/>
       <c r="E20" s="37" t="n"/>
       <c r="F20" s="37" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
       <c r="C21" s="37" t="n"/>
       <c r="D21" s="37" t="n"/>
       <c r="E21" s="37" t="n"/>
       <c r="F21" s="37" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
       <c r="C22" s="37" t="n"/>
       <c r="D22" s="37" t="n"/>
       <c r="E22" s="37" t="n"/>
       <c r="F22" s="37" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
       <c r="C23" s="37" t="n"/>
       <c r="D23" s="37" t="n"/>
       <c r="E23" s="37" t="n"/>
       <c r="F23" s="37" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="B24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
       <c r="C24" s="37" t="n"/>
       <c r="D24" s="37" t="n"/>
       <c r="E24" s="37" t="n"/>
@@ -5438,7 +5960,7 @@
     <row r="26" ht="33" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>The book grows from May. Moderate falls steadily, and August also has slightly short alert data ('A1 rules').</t>
+          <t>The book grows from May. Moderate falls steadily, and August also has slightly short alert data ('Results').</t>
         </is>
       </c>
     </row>
@@ -5449,5 +5971,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/ability/a1_ability_reference.xlsx
+++ b/docs/ability/a1_ability_reference.xlsx
@@ -640,6 +640,189 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Retail loans: share of accounts by state</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="percentStacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!C19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D32"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$20:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$C$20:$C$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!D19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="8BC34A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$20:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$D$20:$D$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!E19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="D9652B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$20:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$E$20:$E$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Results trend'!F19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9E9E9E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Results trend'!$A$20:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Results trend'!$F$20:$F$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="0.25"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -649,7 +832,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="5400000" cy="2232000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -659,6 +842,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2232000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -957,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1048,7 +1253,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="11">
         <f>Results!C6</f>
         <v/>
@@ -1068,310 +1273,346 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12">
-        <f>TEXT(Results!B6,"#,##0")&amp;" cards"&amp;IF(Results!E6="",""," · "&amp;TEXT(Results!E6,"#,##0")&amp;" loans")</f>
+        <f>TEXT(Results!B6,"#,##0")&amp;" credit cards"</f>
         <v/>
       </c>
       <c r="B11" s="12">
-        <f>TEXT(Results!B7,"#,##0")&amp;" cards"&amp;IF(Results!E7="",""," · "&amp;TEXT(Results!E7,"#,##0")&amp;" loans")</f>
+        <f>TEXT(Results!B7,"#,##0")&amp;" credit cards"</f>
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>TEXT(Results!B8,"#,##0")&amp;" cards"&amp;IF(Results!E8="",""," · "&amp;TEXT(Results!E8,"#,##0")&amp;" loans")</f>
+        <f>TEXT(Results!B8,"#,##0")&amp;" credit cards"</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>TEXT(Results!B9,"#,##0")&amp;" cards"&amp;IF(Results!E9="",""," · "&amp;TEXT(Results!E9,"#,##0")&amp;" loans")</f>
+        <f>TEXT(Results!B9,"#,##0")&amp;" credit cards"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="11">
+        <f>Results!E6</f>
+        <v/>
+      </c>
+      <c r="B12" s="11">
+        <f>Results!E7</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>Results!E8</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>Results!E9</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="12">
+        <f>TEXT(Results!D6,"#,##0")&amp;" retail loans"</f>
+        <v/>
+      </c>
+      <c r="B13" s="12">
+        <f>TEXT(Results!D7,"#,##0")&amp;" retail loans"</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>TEXT(Results!D8,"#,##0")&amp;" retail loans"</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>TEXT(Results!D9,"#,##0")&amp;" retail loans"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>States</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>In plain words</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="17" ht="33" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>4 points and no distress</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Regular income and a buffer, both confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46.5" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>2–3 points and no distress, or 4 points with distress</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>One side confirmed, or both partly; or everything in place but a payment just failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="33" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>0–1 points, or under 4 points with distress</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>What we can see shows little or nothing to pay with.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="33" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>Regular income and a buffer, both confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46.5" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>0 points, no distress, and no CASA with us or a dormant one</t>
+          <t>2–3 points and no distress, or 4 points with distress</t>
         </is>
       </c>
       <c r="C18" s="14" t="n"/>
       <c r="D18" s="16" t="inlineStr">
         <is>
+          <t>One side confirmed, or both partly; or everything in place but a payment just failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>0–1 points, or under 4 points with distress</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>What we can see shows little or nothing to pay with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>0 points, no distress, and no CASA with us or a dormant one</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
           <t>We cannot see the customer's money.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>State map: income points + liquidity points, then distress</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>No distress</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Liquidity Adequate</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Liquidity Weak</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Liquidity None</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Income Stable</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Income Weak</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
+          <t>Income Stable</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Income Weak</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
           <t>Income None</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Low (Unknown if CASA dormant or absent)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>With distress</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Liquidity Adequate</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Liquidity Weak</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Liquidity None</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>Income Stable</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>Income Weak</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
+          <t>Income Stable</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Income Weak</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
           <t>Income None</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Rules: 'Logic'. Which rule gave each state: 'Results detail'. What we can see of the customer: 'Results summaries'.</t>
         </is>
@@ -1381,13 +1622,13 @@
   <mergeCells count="10">
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2981,7 +3222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3078,22 +3319,30 @@
         <f>IF(OR(B6="",N(B$10)=0),"",B6/B$10)</f>
         <v/>
       </c>
-      <c r="D6" s="32" t="n"/>
+      <c r="D6" s="32" t="n">
+        <v>11</v>
+      </c>
       <c r="E6" s="33">
         <f>IF(OR(D6="",N(D$10)=0),"",D6/D$10)</f>
         <v/>
       </c>
-      <c r="F6" s="32" t="n"/>
+      <c r="F6" s="32" t="n">
+        <v>6</v>
+      </c>
       <c r="G6" s="33">
         <f>IF(OR(F6="",N(F$10)=0),"",F6/F$10)</f>
         <v/>
       </c>
-      <c r="H6" s="32" t="n"/>
+      <c r="H6" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="I6" s="33">
         <f>IF(OR(H6="",N(H$10)=0),"",H6/H$10)</f>
         <v/>
       </c>
-      <c r="J6" s="32" t="n"/>
+      <c r="J6" s="32" t="n">
+        <v>2</v>
+      </c>
       <c r="K6" s="33">
         <f>IF(OR(J6="",N(J$10)=0),"",J6/J$10)</f>
         <v/>
@@ -3112,22 +3361,30 @@
         <f>IF(OR(B7="",N(B$10)=0),"",B7/B$10)</f>
         <v/>
       </c>
-      <c r="D7" s="32" t="n"/>
+      <c r="D7" s="32" t="n">
+        <v>358</v>
+      </c>
       <c r="E7" s="33">
         <f>IF(OR(D7="",N(D$10)=0),"",D7/D$10)</f>
         <v/>
       </c>
-      <c r="F7" s="32" t="n"/>
+      <c r="F7" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="G7" s="33">
         <f>IF(OR(F7="",N(F$10)=0),"",F7/F$10)</f>
         <v/>
       </c>
-      <c r="H7" s="32" t="n"/>
+      <c r="H7" s="32" t="n">
+        <v>134</v>
+      </c>
       <c r="I7" s="33">
         <f>IF(OR(H7="",N(H$10)=0),"",H7/H$10)</f>
         <v/>
       </c>
-      <c r="J7" s="32" t="n"/>
+      <c r="J7" s="32" t="n">
+        <v>124</v>
+      </c>
       <c r="K7" s="33">
         <f>IF(OR(J7="",N(J$10)=0),"",J7/J$10)</f>
         <v/>
@@ -3146,22 +3403,30 @@
         <f>IF(OR(B8="",N(B$10)=0),"",B8/B$10)</f>
         <v/>
       </c>
-      <c r="D8" s="32" t="n"/>
+      <c r="D8" s="32" t="n">
+        <v>1837</v>
+      </c>
       <c r="E8" s="33">
         <f>IF(OR(D8="",N(D$10)=0),"",D8/D$10)</f>
         <v/>
       </c>
-      <c r="F8" s="32" t="n"/>
+      <c r="F8" s="32" t="n">
+        <v>593</v>
+      </c>
       <c r="G8" s="33">
         <f>IF(OR(F8="",N(F$10)=0),"",F8/F$10)</f>
         <v/>
       </c>
-      <c r="H8" s="32" t="n"/>
+      <c r="H8" s="32" t="n">
+        <v>608</v>
+      </c>
       <c r="I8" s="33">
         <f>IF(OR(H8="",N(H$10)=0),"",H8/H$10)</f>
         <v/>
       </c>
-      <c r="J8" s="32" t="n"/>
+      <c r="J8" s="32" t="n">
+        <v>636</v>
+      </c>
       <c r="K8" s="33">
         <f>IF(OR(J8="",N(J$10)=0),"",J8/J$10)</f>
         <v/>
@@ -3180,22 +3445,30 @@
         <f>IF(OR(B9="",N(B$10)=0),"",B9/B$10)</f>
         <v/>
       </c>
-      <c r="D9" s="32" t="n"/>
+      <c r="D9" s="32" t="n">
+        <v>1779</v>
+      </c>
       <c r="E9" s="33">
         <f>IF(OR(D9="",N(D$10)=0),"",D9/D$10)</f>
         <v/>
       </c>
-      <c r="F9" s="32" t="n"/>
+      <c r="F9" s="32" t="n">
+        <v>698</v>
+      </c>
       <c r="G9" s="33">
         <f>IF(OR(F9="",N(F$10)=0),"",F9/F$10)</f>
         <v/>
       </c>
-      <c r="H9" s="32" t="n"/>
+      <c r="H9" s="32" t="n">
+        <v>479</v>
+      </c>
       <c r="I9" s="33">
         <f>IF(OR(H9="",N(H$10)=0),"",H9/H$10)</f>
         <v/>
       </c>
-      <c r="J9" s="32" t="n"/>
+      <c r="J9" s="32" t="n">
+        <v>602</v>
+      </c>
       <c r="K9" s="33">
         <f>IF(OR(J9="",N(J$10)=0),"",J9/J$10)</f>
         <v/>
@@ -3260,7 +3533,7 @@
     <row r="13" ht="33" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>A customer with fewer alerts in the window than before can look like a fall: 912 accounts reach the window total but fail the 25% check. Some are real falls; the data cannot yet split them.</t>
+          <t>A customer with fewer alerts in the window than before can look like a fall: 912 card and 86 loan accounts reach the window total but fail the 25% check. Some are real falls; the data cannot yet split them.</t>
         </is>
       </c>
     </row>
@@ -3288,21 +3561,37 @@
     <row r="17" ht="33" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Internal salary and balances cover the PRB, PSB and PB segments (95% of base customers). Internal salary history starts in September 2024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+          <t>Every loan customer shows a CASA transaction, so No CASA never fires on loans and all their Unknowns are dormant. The transaction can be just the bank collecting the instalment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Loan thresholds are higher: one instalment (median AED 2,389) against the card's oldest overdue amount (median AED 837), so a loan salary must cover more to count as Stable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Internal salary and balances cover the PRB, PSB and PB segments (95% of card customers). Internal salary history starts in September 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Which rule gave each state: 'Results detail'. Coverage of salary, CASA and bureau: 'Results summaries'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A18:K18"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A21:K21"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="F5:G5"/>
@@ -3395,7 +3684,9 @@
         <v>19292</v>
       </c>
       <c r="C6" s="36" t="n"/>
-      <c r="D6" s="32" t="n"/>
+      <c r="D6" s="32" t="n">
+        <v>3985</v>
+      </c>
       <c r="E6" s="36" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
@@ -3411,7 +3702,9 @@
         <f>IF(OR(B7="",N(B$6)=0),"",B7/B$6)</f>
         <v/>
       </c>
-      <c r="D7" s="32" t="n"/>
+      <c r="D7" s="32" t="n">
+        <v>41</v>
+      </c>
       <c r="E7" s="33">
         <f>IF(OR(D7="",N(D$6)=0),"",D7/D$6)</f>
         <v/>
@@ -3430,7 +3723,9 @@
         <f>IF(OR(B8="",N(B$6)=0),"",B8/B$6)</f>
         <v/>
       </c>
-      <c r="D8" s="32" t="n"/>
+      <c r="D8" s="32" t="n">
+        <v>307</v>
+      </c>
       <c r="E8" s="33">
         <f>IF(OR(D8="",N(D$6)=0),"",D8/D$6)</f>
         <v/>
@@ -3449,7 +3744,9 @@
         <f>IF(OR(B9="",N(B$6)=0),"",B9/B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="32" t="n"/>
+      <c r="D9" s="32" t="n">
+        <v>13</v>
+      </c>
       <c r="E9" s="33">
         <f>IF(OR(D9="",N(D$6)=0),"",D9/D$6)</f>
         <v/>
@@ -3468,7 +3765,9 @@
         <f>IF(OR(B10="",N(B$6)=0),"",B10/B$6)</f>
         <v/>
       </c>
-      <c r="D10" s="32" t="n"/>
+      <c r="D10" s="32" t="n">
+        <v>143</v>
+      </c>
       <c r="E10" s="33">
         <f>IF(OR(D10="",N(D$6)=0),"",D10/D$6)</f>
         <v/>
@@ -3487,7 +3786,9 @@
         <f>IF(OR(B11="",N(B$6)=0),"",B11/B$6)</f>
         <v/>
       </c>
-      <c r="D11" s="32" t="n"/>
+      <c r="D11" s="32" t="n">
+        <v>231</v>
+      </c>
       <c r="E11" s="33">
         <f>IF(OR(D11="",N(D$6)=0),"",D11/D$6)</f>
         <v/>
@@ -3506,7 +3807,9 @@
         <f>IF(OR(B12="",N(B$6)=0),"",B12/B$6)</f>
         <v/>
       </c>
-      <c r="D12" s="32" t="n"/>
+      <c r="D12" s="32" t="n">
+        <v>8</v>
+      </c>
       <c r="E12" s="33">
         <f>IF(OR(D12="",N(D$6)=0),"",D12/D$6)</f>
         <v/>
@@ -3525,7 +3828,9 @@
         <f>IF(OR(B13="",N(B$6)=0),"",B13/B$6)</f>
         <v/>
       </c>
-      <c r="D13" s="32" t="n"/>
+      <c r="D13" s="32" t="n">
+        <v>3242</v>
+      </c>
       <c r="E13" s="33">
         <f>IF(OR(D13="",N(D$6)=0),"",D13/D$6)</f>
         <v/>
@@ -3578,7 +3883,9 @@
         <f>IF(OR(B17="",N(B$6)=0),"",B17/B$6)</f>
         <v/>
       </c>
-      <c r="D17" s="32" t="n"/>
+      <c r="D17" s="32" t="n">
+        <v>37</v>
+      </c>
       <c r="E17" s="33">
         <f>IF(OR(D17="",N(D$6)=0),"",D17/D$6)</f>
         <v/>
@@ -3597,7 +3904,9 @@
         <f>IF(OR(B18="",N(B$6)=0),"",B18/B$6)</f>
         <v/>
       </c>
-      <c r="D18" s="32" t="n"/>
+      <c r="D18" s="32" t="n">
+        <v>161</v>
+      </c>
       <c r="E18" s="33">
         <f>IF(OR(D18="",N(D$6)=0),"",D18/D$6)</f>
         <v/>
@@ -3616,7 +3925,9 @@
         <f>IF(OR(B19="",N(B$6)=0),"",B19/B$6)</f>
         <v/>
       </c>
-      <c r="D19" s="32" t="n"/>
+      <c r="D19" s="32" t="n">
+        <v>122</v>
+      </c>
       <c r="E19" s="33">
         <f>IF(OR(D19="",N(D$6)=0),"",D19/D$6)</f>
         <v/>
@@ -3635,7 +3946,9 @@
         <f>IF(OR(B20="",N(B$6)=0),"",B20/B$6)</f>
         <v/>
       </c>
-      <c r="D20" s="32" t="n"/>
+      <c r="D20" s="32" t="n">
+        <v>86</v>
+      </c>
       <c r="E20" s="33">
         <f>IF(OR(D20="",N(D$6)=0),"",D20/D$6)</f>
         <v/>
@@ -3654,7 +3967,9 @@
         <f>IF(OR(B21="",N(B$6)=0),"",B21/B$6)</f>
         <v/>
       </c>
-      <c r="D21" s="32" t="n"/>
+      <c r="D21" s="32" t="n">
+        <v>153</v>
+      </c>
       <c r="E21" s="33">
         <f>IF(OR(D21="",N(D$6)=0),"",D21/D$6)</f>
         <v/>
@@ -3707,7 +4022,9 @@
         <f>IF(OR(B25="",N(B$6)=0),"",B25/B$6)</f>
         <v/>
       </c>
-      <c r="D25" s="32" t="n"/>
+      <c r="D25" s="32" t="n">
+        <v>46</v>
+      </c>
       <c r="E25" s="33">
         <f>IF(OR(D25="",N(D$6)=0),"",D25/D$6)</f>
         <v/>
@@ -3726,7 +4043,9 @@
         <f>IF(OR(B26="",N(B$6)=0),"",B26/B$6)</f>
         <v/>
       </c>
-      <c r="D26" s="32" t="n"/>
+      <c r="D26" s="32" t="n">
+        <v>11</v>
+      </c>
       <c r="E26" s="33">
         <f>IF(OR(D26="",N(D$6)=0),"",D26/D$6)</f>
         <v/>
@@ -3745,7 +4064,9 @@
         <f>IF(OR(B27="",N(B$6)=0),"",B27/B$6)</f>
         <v/>
       </c>
-      <c r="D27" s="32" t="n"/>
+      <c r="D27" s="32" t="n">
+        <v>291</v>
+      </c>
       <c r="E27" s="33">
         <f>IF(OR(D27="",N(D$6)=0),"",D27/D$6)</f>
         <v/>
@@ -3764,7 +4085,9 @@
         <f>IF(OR(B28="",N(B$6)=0),"",B28/B$6)</f>
         <v/>
       </c>
-      <c r="D28" s="32" t="n"/>
+      <c r="D28" s="32" t="n">
+        <v>14</v>
+      </c>
       <c r="E28" s="33">
         <f>IF(OR(D28="",N(D$6)=0),"",D28/D$6)</f>
         <v/>
@@ -3783,7 +4106,9 @@
         <f>IF(OR(B29="",N(B$6)=0),"",B29/B$6)</f>
         <v/>
       </c>
-      <c r="D29" s="32" t="n"/>
+      <c r="D29" s="32" t="n">
+        <v>14</v>
+      </c>
       <c r="E29" s="33">
         <f>IF(OR(D29="",N(D$6)=0),"",D29/D$6)</f>
         <v/>
@@ -3802,7 +4127,9 @@
         <f>IF(OR(B30="",N(B$6)=0),"",B30/B$6)</f>
         <v/>
       </c>
-      <c r="D30" s="32" t="n"/>
+      <c r="D30" s="32" t="n">
+        <v>3609</v>
+      </c>
       <c r="E30" s="33">
         <f>IF(OR(D30="",N(D$6)=0),"",D30/D$6)</f>
         <v/>
@@ -3855,7 +4182,9 @@
         <f>IF(OR(B34="",N(B$6)=0),"",B34/B$6)</f>
         <v/>
       </c>
-      <c r="D34" s="32" t="n"/>
+      <c r="D34" s="32" t="n">
+        <v>3261</v>
+      </c>
       <c r="E34" s="33">
         <f>IF(OR(D34="",N(D$6)=0),"",D34/D$6)</f>
         <v/>
@@ -3874,7 +4203,9 @@
         <f>IF(OR(B35="",N(B$6)=0),"",B35/B$6)</f>
         <v/>
       </c>
-      <c r="D35" s="32" t="n"/>
+      <c r="D35" s="32" t="n">
+        <v>282</v>
+      </c>
       <c r="E35" s="33">
         <f>IF(OR(D35="",N(D$6)=0),"",D35/D$6)</f>
         <v/>
@@ -3893,7 +4224,9 @@
         <f>IF(OR(B36="",N(B$6)=0),"",B36/B$6)</f>
         <v/>
       </c>
-      <c r="D36" s="32" t="n"/>
+      <c r="D36" s="32" t="n">
+        <v>189</v>
+      </c>
       <c r="E36" s="33">
         <f>IF(OR(D36="",N(D$6)=0),"",D36/D$6)</f>
         <v/>
@@ -3912,7 +4245,9 @@
         <f>IF(OR(B37="",N(B$6)=0),"",B37/B$6)</f>
         <v/>
       </c>
-      <c r="D37" s="32" t="n"/>
+      <c r="D37" s="32" t="n">
+        <v>184</v>
+      </c>
       <c r="E37" s="33">
         <f>IF(OR(D37="",N(D$6)=0),"",D37/D$6)</f>
         <v/>
@@ -3931,7 +4266,9 @@
         <f>IF(OR(B38="",N(B$6)=0),"",B38/B$6)</f>
         <v/>
       </c>
-      <c r="D38" s="32" t="n"/>
+      <c r="D38" s="32" t="n">
+        <v>69</v>
+      </c>
       <c r="E38" s="33">
         <f>IF(OR(D38="",N(D$6)=0),"",D38/D$6)</f>
         <v/>
@@ -3984,7 +4321,9 @@
         <f>IF(OR(B42="",N(B$6)=0),"",B42/B$6)</f>
         <v/>
       </c>
-      <c r="D42" s="32" t="n"/>
+      <c r="D42" s="32" t="n">
+        <v>11</v>
+      </c>
       <c r="E42" s="33">
         <f>IF(OR(D42="",N(D$6)=0),"",D42/D$6)</f>
         <v/>
@@ -4003,7 +4342,9 @@
         <f>IF(OR(B43="",N(B$6)=0),"",B43/B$6)</f>
         <v/>
       </c>
-      <c r="D43" s="32" t="n"/>
+      <c r="D43" s="32" t="n">
+        <v>271</v>
+      </c>
       <c r="E43" s="33">
         <f>IF(OR(D43="",N(D$6)=0),"",D43/D$6)</f>
         <v/>
@@ -4022,7 +4363,9 @@
         <f>IF(OR(B44="",N(B$6)=0),"",B44/B$6)</f>
         <v/>
       </c>
-      <c r="D44" s="32" t="n"/>
+      <c r="D44" s="32" t="n">
+        <v>23</v>
+      </c>
       <c r="E44" s="33">
         <f>IF(OR(D44="",N(D$6)=0),"",D44/D$6)</f>
         <v/>
@@ -4041,7 +4384,9 @@
         <f>IF(OR(B45="",N(B$6)=0),"",B45/B$6)</f>
         <v/>
       </c>
-      <c r="D45" s="32" t="n"/>
+      <c r="D45" s="32" t="n">
+        <v>19</v>
+      </c>
       <c r="E45" s="33">
         <f>IF(OR(D45="",N(D$6)=0),"",D45/D$6)</f>
         <v/>
@@ -4060,7 +4405,9 @@
         <f>IF(OR(B46="",N(B$6)=0),"",B46/B$6)</f>
         <v/>
       </c>
-      <c r="D46" s="32" t="n"/>
+      <c r="D46" s="32" t="n">
+        <v>39</v>
+      </c>
       <c r="E46" s="33">
         <f>IF(OR(D46="",N(D$6)=0),"",D46/D$6)</f>
         <v/>
@@ -4079,7 +4426,9 @@
         <f>IF(OR(B47="",N(B$6)=0),"",B47/B$6)</f>
         <v/>
       </c>
-      <c r="D47" s="32" t="n"/>
+      <c r="D47" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="E47" s="33">
         <f>IF(OR(D47="",N(D$6)=0),"",D47/D$6)</f>
         <v/>
@@ -4098,7 +4447,9 @@
         <f>IF(OR(B48="",N(B$6)=0),"",B48/B$6)</f>
         <v/>
       </c>
-      <c r="D48" s="32" t="n"/>
+      <c r="D48" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="E48" s="33">
         <f>IF(OR(D48="",N(D$6)=0),"",D48/D$6)</f>
         <v/>
@@ -4151,7 +4502,9 @@
         <f>IF(OR(B52="",N(B$6)=0),"",B52/B$6)</f>
         <v/>
       </c>
-      <c r="D52" s="32" t="n"/>
+      <c r="D52" s="32" t="n">
+        <v>559</v>
+      </c>
       <c r="E52" s="33">
         <f>IF(OR(D52="",N(D$6)=0),"",D52/D$6)</f>
         <v/>
@@ -4170,7 +4523,9 @@
         <f>IF(OR(B53="",N(B$6)=0),"",B53/B$6)</f>
         <v/>
       </c>
-      <c r="D53" s="32" t="n"/>
+      <c r="D53" s="32" t="n">
+        <v>656</v>
+      </c>
       <c r="E53" s="33">
         <f>IF(OR(D53="",N(D$6)=0),"",D53/D$6)</f>
         <v/>
@@ -4189,7 +4544,9 @@
         <f>IF(OR(B54="",N(B$6)=0),"",B54/B$6)</f>
         <v/>
       </c>
-      <c r="D54" s="32" t="n"/>
+      <c r="D54" s="32" t="n">
+        <v>539</v>
+      </c>
       <c r="E54" s="33">
         <f>IF(OR(D54="",N(D$6)=0),"",D54/D$6)</f>
         <v/>
@@ -4208,7 +4565,9 @@
         <f>IF(OR(B55="",N(B$6)=0),"",B55/B$6)</f>
         <v/>
       </c>
-      <c r="D55" s="32" t="n"/>
+      <c r="D55" s="32" t="n">
+        <v>83</v>
+      </c>
       <c r="E55" s="33">
         <f>IF(OR(D55="",N(D$6)=0),"",D55/D$6)</f>
         <v/>
@@ -4261,7 +4620,9 @@
         <f>IF(OR(B59="",N(B$6)=0),"",B59/B$6)</f>
         <v/>
       </c>
-      <c r="D59" s="32" t="n"/>
+      <c r="D59" s="32" t="n">
+        <v>1779</v>
+      </c>
       <c r="E59" s="33">
         <f>IF(OR(D59="",N(D$6)=0),"",D59/D$6)</f>
         <v/>
@@ -4280,16 +4641,18 @@
         <f>IF(OR(B60="",N(B$6)=0),"",B60/B$6)</f>
         <v/>
       </c>
-      <c r="D60" s="32" t="n"/>
+      <c r="D60" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="E60" s="33">
         <f>IF(OR(D60="",N(D$6)=0),"",D60/D$6)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="33" customHeight="1">
+    <row r="62" ht="46.5" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>The AECB Stable and Weak rows include accounts with internal salary too. A card payment can sit beside a sufficient balance, so the arms overlap in the second Adequate row.</t>
+          <t>The AECB Stable and Weak rows include accounts with internal salary too; on loans AECB also includes the salary on the loan's own bureau pull. A card payment can sit beside a sufficient balance, so the arms overlap in the second Adequate row.</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4504,7 +4867,9 @@
         <v>19292</v>
       </c>
       <c r="C6" s="36" t="n"/>
-      <c r="D6" s="32" t="n"/>
+      <c r="D6" s="32" t="n">
+        <v>3985</v>
+      </c>
       <c r="E6" s="36" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
@@ -4520,7 +4885,9 @@
         <f>IF(OR(B7="",N(B$6)=0),"",B7/B$6)</f>
         <v/>
       </c>
-      <c r="D7" s="32" t="n"/>
+      <c r="D7" s="32" t="n">
+        <v>1332</v>
+      </c>
       <c r="E7" s="33">
         <f>IF(OR(D7="",N(D$6)=0),"",D7/D$6)</f>
         <v/>
@@ -4539,7 +4906,9 @@
         <f>IF(OR(B8="",N(B$6)=0),"",B8/B$6)</f>
         <v/>
       </c>
-      <c r="D8" s="32" t="n"/>
+      <c r="D8" s="32" t="n">
+        <v>2653</v>
+      </c>
       <c r="E8" s="33">
         <f>IF(OR(D8="",N(D$6)=0),"",D8/D$6)</f>
         <v/>
@@ -4558,7 +4927,9 @@
         <f>IF(OR(B9="",N(B$6)=0),"",B9/B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="32" t="n"/>
+      <c r="D9" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" s="33">
         <f>IF(OR(D9="",N(D$6)=0),"",D9/D$6)</f>
         <v/>
@@ -4611,7 +4982,9 @@
         <f>IF(OR(B13="",N(B$6)=0),"",B13/B$6)</f>
         <v/>
       </c>
-      <c r="D13" s="32" t="n"/>
+      <c r="D13" s="32" t="n">
+        <v>205</v>
+      </c>
       <c r="E13" s="33">
         <f>IF(OR(D13="",N(D$6)=0),"",D13/D$6)</f>
         <v/>
@@ -4630,7 +5003,9 @@
         <f>IF(OR(B14="",N(B$6)=0),"",B14/B$6)</f>
         <v/>
       </c>
-      <c r="D14" s="32" t="n"/>
+      <c r="D14" s="32" t="n">
+        <v>1146</v>
+      </c>
       <c r="E14" s="33">
         <f>IF(OR(D14="",N(D$6)=0),"",D14/D$6)</f>
         <v/>
@@ -4649,7 +5024,9 @@
         <f>IF(OR(B15="",N(B$6)=0),"",B15/B$6)</f>
         <v/>
       </c>
-      <c r="D15" s="32" t="n"/>
+      <c r="D15" s="32" t="n">
+        <v>888</v>
+      </c>
       <c r="E15" s="33">
         <f>IF(OR(D15="",N(D$6)=0),"",D15/D$6)</f>
         <v/>
@@ -4668,7 +5045,9 @@
         <f>IF(OR(B16="",N(B$6)=0),"",B16/B$6)</f>
         <v/>
       </c>
-      <c r="D16" s="32" t="n"/>
+      <c r="D16" s="32" t="n">
+        <v>528</v>
+      </c>
       <c r="E16" s="33">
         <f>IF(OR(D16="",N(D$6)=0),"",D16/D$6)</f>
         <v/>
@@ -4687,7 +5066,9 @@
         <f>IF(OR(B17="",N(B$6)=0),"",B17/B$6)</f>
         <v/>
       </c>
-      <c r="D17" s="32" t="n"/>
+      <c r="D17" s="32" t="n">
+        <v>1218</v>
+      </c>
       <c r="E17" s="33">
         <f>IF(OR(D17="",N(D$6)=0),"",D17/D$6)</f>
         <v/>
@@ -4740,7 +5121,9 @@
         <f>IF(OR(B21="",N(B$6)=0),"",B21/B$6)</f>
         <v/>
       </c>
-      <c r="D21" s="32" t="n"/>
+      <c r="D21" s="32" t="n">
+        <v>461</v>
+      </c>
       <c r="E21" s="33">
         <f>IF(OR(D21="",N(D$6)=0),"",D21/D$6)</f>
         <v/>
@@ -4759,7 +5142,9 @@
         <f>IF(OR(B22="",N(B$6)=0),"",B22/B$6)</f>
         <v/>
       </c>
-      <c r="D22" s="32" t="n"/>
+      <c r="D22" s="32" t="n">
+        <v>262</v>
+      </c>
       <c r="E22" s="33">
         <f>IF(OR(D22="",N(D$6)=0),"",D22/D$6)</f>
         <v/>
@@ -4778,7 +5163,9 @@
         <f>IF(OR(B23="",N(B$6)=0),"",B23/B$6)</f>
         <v/>
       </c>
-      <c r="D23" s="32" t="n"/>
+      <c r="D23" s="32" t="n">
+        <v>230</v>
+      </c>
       <c r="E23" s="33">
         <f>IF(OR(D23="",N(D$6)=0),"",D23/D$6)</f>
         <v/>
@@ -4797,7 +5184,9 @@
         <f>IF(OR(B24="",N(B$6)=0),"",B24/B$6)</f>
         <v/>
       </c>
-      <c r="D24" s="32" t="n"/>
+      <c r="D24" s="32" t="n">
+        <v>274</v>
+      </c>
       <c r="E24" s="33">
         <f>IF(OR(D24="",N(D$6)=0),"",D24/D$6)</f>
         <v/>
@@ -4816,7 +5205,9 @@
         <f>IF(OR(B25="",N(B$6)=0),"",B25/B$6)</f>
         <v/>
       </c>
-      <c r="D25" s="32" t="n"/>
+      <c r="D25" s="32" t="n">
+        <v>285</v>
+      </c>
       <c r="E25" s="33">
         <f>IF(OR(D25="",N(D$6)=0),"",D25/D$6)</f>
         <v/>
@@ -4835,7 +5226,9 @@
         <f>IF(OR(B26="",N(B$6)=0),"",B26/B$6)</f>
         <v/>
       </c>
-      <c r="D26" s="32" t="n"/>
+      <c r="D26" s="32" t="n">
+        <v>2310</v>
+      </c>
       <c r="E26" s="33">
         <f>IF(OR(D26="",N(D$6)=0),"",D26/D$6)</f>
         <v/>
@@ -4854,7 +5247,9 @@
         <f>IF(OR(B27="",N(B$6)=0),"",B27/B$6)</f>
         <v/>
       </c>
-      <c r="D27" s="32" t="n"/>
+      <c r="D27" s="32" t="n">
+        <v>163</v>
+      </c>
       <c r="E27" s="33">
         <f>IF(OR(D27="",N(D$6)=0),"",D27/D$6)</f>
         <v/>
@@ -4907,7 +5302,9 @@
         <f>IF(OR(B31="",N(B$6)=0),"",B31/B$6)</f>
         <v/>
       </c>
-      <c r="D31" s="32" t="n"/>
+      <c r="D31" s="32" t="n">
+        <v>645</v>
+      </c>
       <c r="E31" s="33">
         <f>IF(OR(D31="",N(D$6)=0),"",D31/D$6)</f>
         <v/>
@@ -4926,7 +5323,9 @@
         <f>IF(OR(B32="",N(B$6)=0),"",B32/B$6)</f>
         <v/>
       </c>
-      <c r="D32" s="32" t="n"/>
+      <c r="D32" s="32" t="n">
+        <v>2615</v>
+      </c>
       <c r="E32" s="33">
         <f>IF(OR(D32="",N(D$6)=0),"",D32/D$6)</f>
         <v/>
@@ -4945,7 +5344,9 @@
         <f>IF(OR(B33="",N(B$6)=0),"",B33/B$6)</f>
         <v/>
       </c>
-      <c r="D33" s="32" t="n"/>
+      <c r="D33" s="32" t="n">
+        <v>725</v>
+      </c>
       <c r="E33" s="33">
         <f>IF(OR(D33="",N(D$6)=0),"",D33/D$6)</f>
         <v/>
@@ -4998,7 +5399,9 @@
         <f>IF(OR(B37="",N(B$6)=0),"",B37/B$6)</f>
         <v/>
       </c>
-      <c r="D37" s="32" t="n"/>
+      <c r="D37" s="32" t="n">
+        <v>1025</v>
+      </c>
       <c r="E37" s="33">
         <f>IF(OR(D37="",N(D$6)=0),"",D37/D$6)</f>
         <v/>
@@ -5017,7 +5420,9 @@
         <f>IF(OR(B38="",N(B$6)=0),"",B38/B$6)</f>
         <v/>
       </c>
-      <c r="D38" s="32" t="n"/>
+      <c r="D38" s="32" t="n">
+        <v>72</v>
+      </c>
       <c r="E38" s="33">
         <f>IF(OR(D38="",N(D$6)=0),"",D38/D$6)</f>
         <v/>
@@ -5036,7 +5441,9 @@
         <f>IF(OR(B39="",N(B$6)=0),"",B39/B$6)</f>
         <v/>
       </c>
-      <c r="D39" s="32" t="n"/>
+      <c r="D39" s="32" t="n">
+        <v>49</v>
+      </c>
       <c r="E39" s="33">
         <f>IF(OR(D39="",N(D$6)=0),"",D39/D$6)</f>
         <v/>
@@ -5055,7 +5462,9 @@
         <f>IF(OR(B40="",N(B$6)=0),"",B40/B$6)</f>
         <v/>
       </c>
-      <c r="D40" s="32" t="n"/>
+      <c r="D40" s="32" t="n">
+        <v>2839</v>
+      </c>
       <c r="E40" s="33">
         <f>IF(OR(D40="",N(D$6)=0),"",D40/D$6)</f>
         <v/>
@@ -5108,7 +5517,9 @@
         <f>IF(OR(B44="",N(B$6)=0),"",B44/B$6)</f>
         <v/>
       </c>
-      <c r="D44" s="32" t="n"/>
+      <c r="D44" s="32" t="n">
+        <v>158</v>
+      </c>
       <c r="E44" s="33">
         <f>IF(OR(D44="",N(D$6)=0),"",D44/D$6)</f>
         <v/>
@@ -5127,7 +5538,9 @@
         <f>IF(OR(B45="",N(B$6)=0),"",B45/B$6)</f>
         <v/>
       </c>
-      <c r="D45" s="32" t="n"/>
+      <c r="D45" s="32" t="n">
+        <v>193</v>
+      </c>
       <c r="E45" s="33">
         <f>IF(OR(D45="",N(D$6)=0),"",D45/D$6)</f>
         <v/>
@@ -5146,7 +5559,9 @@
         <f>IF(OR(B46="",N(B$6)=0),"",B46/B$6)</f>
         <v/>
       </c>
-      <c r="D46" s="32" t="n"/>
+      <c r="D46" s="32" t="n">
+        <v>1410</v>
+      </c>
       <c r="E46" s="33">
         <f>IF(OR(D46="",N(D$6)=0),"",D46/D$6)</f>
         <v/>
@@ -5165,7 +5580,9 @@
         <f>IF(OR(B47="",N(B$6)=0),"",B47/B$6)</f>
         <v/>
       </c>
-      <c r="D47" s="32" t="n"/>
+      <c r="D47" s="32" t="n">
+        <v>2224</v>
+      </c>
       <c r="E47" s="33">
         <f>IF(OR(D47="",N(D$6)=0),"",D47/D$6)</f>
         <v/>
@@ -5218,34 +5635,25 @@
         <f>IF(OR(B51="",N(B$6)=0),"",B51/B$6)</f>
         <v/>
       </c>
-      <c r="D51" s="32" t="n"/>
+      <c r="D51" s="32" t="n">
+        <v>12</v>
+      </c>
       <c r="E51" s="33">
         <f>IF(OR(D51="",N(D$6)=0),"",D51/D$6)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Internal salary × AECB salary, credit cards</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>See the sheet 'Salary sources'.</t>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Internal salary against AECB salary: 'Salary sources'.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A53:E53"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C9">
     <cfRule type="dataBar" priority="1">
@@ -5385,7 +5793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5403,162 +5811,324 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Accounts by the latest internal salary and the latest AECB salary alert, credit cards, 31 Aug 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr"/>
-      <c r="B4" s="13" t="inlineStr">
+          <t>Accounts by the latest internal salary and the latest AECB salary alert, 31 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Credit cards</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="13" t="inlineStr"/>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>AECB in window</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>AECB 4–6 m</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>AECB 7–12 m</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>AECB 13+ m</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Internal in window</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="n">
-        <v>34</v>
-      </c>
-      <c r="C5" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="E5" s="32" t="n">
-        <v>79</v>
-      </c>
-      <c r="F5" s="32" t="n">
-        <v>298</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>Internal 4–6 m</t>
+          <t>Internal in window</t>
         </is>
       </c>
       <c r="B6" s="32" t="n">
-        <v>349</v>
+        <v>34</v>
       </c>
       <c r="C6" s="32" t="n">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>2237</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Internal 7–12 m</t>
+          <t>Internal 4–6 m</t>
         </is>
       </c>
       <c r="B7" s="32" t="n">
-        <v>438</v>
+        <v>349</v>
       </c>
       <c r="C7" s="32" t="n">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>2389</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Internal 13–24 m</t>
+          <t>Internal 7–12 m</t>
         </is>
       </c>
       <c r="B8" s="32" t="n">
-        <v>268</v>
+        <v>438</v>
       </c>
       <c r="C8" s="32" t="n">
-        <v>167</v>
+        <v>265</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>1104</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
+          <t>Internal 13–24 m</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n">
+        <v>268</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>167</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>213</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
           <t>No internal in 24 m</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
+      <c r="B10" s="32" t="n">
         <v>2640</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C10" s="32" t="n">
         <v>1794</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D10" s="32" t="n">
         <v>1609</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E10" s="32" t="n">
         <v>1350</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F10" s="32" t="n">
         <v>2825</v>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>'Never' = no AECB salary alert of AED 1,000 or more, with or without alert rows. Retail loans follow.</t>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Retail loans</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="13" t="inlineStr"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>AECB in window</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>AECB 4–6 m</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>AECB 7–12 m</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>AECB 13+ m</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Internal in window</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Internal 4–6 m</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="n">
+        <v>93</v>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>47</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>178</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Internal 7–12 m</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n">
+        <v>108</v>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>62</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="E16" s="32" t="n">
+        <v>136</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>Internal 13–24 m</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="n">
+        <v>91</v>
+      </c>
+      <c r="C17" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <v>76</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>No internal in 24 m</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="n">
+        <v>148</v>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>103</v>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>102</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>140</v>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="20" ht="33" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>'Never' = no AECB salary alert of AED 1,000 or more, with or without alert rows. Before the 1-month carry.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5572,7 +6142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5817,157 +6387,237 @@
         <v>0.5608</v>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Retail loans 61–180</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Accounts</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="37" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="37" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
-      </c>
-      <c r="B18" s="32" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="37" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="37" t="n"/>
-      <c r="D19" s="37" t="n"/>
-      <c r="E19" s="37" t="n"/>
-      <c r="F19" s="37" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
-        </is>
-      </c>
-      <c r="B20" s="32" t="n"/>
-      <c r="C20" s="37" t="n"/>
-      <c r="D20" s="37" t="n"/>
-      <c r="E20" s="37" t="n"/>
-      <c r="F20" s="37" t="n"/>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="n">
+        <v>2324</v>
+      </c>
+      <c r="C20" s="37" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="E20" s="37" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="F20" s="37" t="n">
+        <v>0.4122</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="34" t="inlineStr">
         <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="37" t="n"/>
-      <c r="D21" s="37" t="n"/>
-      <c r="E21" s="37" t="n"/>
-      <c r="F21" s="37" t="n"/>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="n">
+        <v>2213</v>
+      </c>
+      <c r="C21" s="37" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="D21" s="37" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="E21" s="37" t="n">
+        <v>0.4424</v>
+      </c>
+      <c r="F21" s="37" t="n">
+        <v>0.4474</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="n"/>
-      <c r="C22" s="37" t="n"/>
-      <c r="D22" s="37" t="n"/>
-      <c r="E22" s="37" t="n"/>
-      <c r="F22" s="37" t="n"/>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="n">
+        <v>2218</v>
+      </c>
+      <c r="C22" s="37" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="D22" s="37" t="n">
+        <v>0.1123</v>
+      </c>
+      <c r="E22" s="37" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="F22" s="37" t="n">
+        <v>0.4274</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="37" t="n"/>
-      <c r="D23" s="37" t="n"/>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="37" t="n"/>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n">
+        <v>2661</v>
+      </c>
+      <c r="C23" s="37" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="D23" s="37" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="E23" s="37" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="F23" s="37" t="n">
+        <v>0.4021</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="34" t="inlineStr">
         <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n">
+        <v>3096</v>
+      </c>
+      <c r="C24" s="37" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="E24" s="37" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="F24" s="37" t="n">
+        <v>0.3928</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="n">
+        <v>3514</v>
+      </c>
+      <c r="C25" s="37" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="D25" s="37" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="E25" s="37" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="F25" s="37" t="n">
+        <v>0.4069</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="n">
+        <v>3728</v>
+      </c>
+      <c r="C26" s="37" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <v>0.09630000000000001</v>
+      </c>
+      <c r="E26" s="37" t="n">
+        <v>0.4742</v>
+      </c>
+      <c r="F26" s="37" t="n">
+        <v>0.4286</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="37" t="n"/>
-      <c r="E24" s="37" t="n"/>
-      <c r="F24" s="37" t="n"/>
-    </row>
-    <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>The book grows from May. Moderate falls steadily, and August also has slightly short alert data ('Results').</t>
+      <c r="B27" s="32" t="n">
+        <v>3985</v>
+      </c>
+      <c r="C27" s="37" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="D27" s="37" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="E27" s="37" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="F27" s="37" t="n">
+        <v>0.4464</v>
+      </c>
+    </row>
+    <row r="29" ht="46.5" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Both books grow from April–May while Moderate falls and Unknown rises from June. August also has slightly short alert data ('Results'). High is too small to read on the charts.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
